--- a/tests/test_files/excel_to_yaml/failures.xlsx
+++ b/tests/test_files/excel_to_yaml/failures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AImperadore\Desktop\EU-SCORES\eu-scores\tests\test_files\excel_to_yaml\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Riccardo\ORIOM\oriom\tests\test_files\excel_to_yaml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896D4F1E-324E-4C43-94EA-E1091266FF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75257A1B-0383-40F8-8CC5-3DF8D55A4F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{52403AFF-FBD8-4761-870C-F1D750C9FAD2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{52403AFF-FBD8-4761-870C-F1D750C9FAD2}"/>
   </bookViews>
   <sheets>
     <sheet name="SA_Scenarios" sheetId="4" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="47">
   <si>
     <t>id</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>ofw_OPm001</t>
+  </si>
+  <si>
+    <t>preferred_day</t>
   </si>
 </sst>
 </file>
@@ -418,9 +421,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -458,7 +461,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -564,7 +567,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -706,7 +709,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -715,15 +718,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F20298EF-E320-4BFA-B2EA-2A0E5C96041A}">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" customWidth="1"/>
-    <col min="10" max="10" width="10.26953125" customWidth="1"/>
-    <col min="12" max="12" width="10.1796875" customWidth="1"/>
-    <col min="13" max="13" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -764,7 +767,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -805,7 +808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -846,7 +849,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -894,19 +897,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CDAEF9-588F-4096-807D-6F3D5943214A}">
-  <dimension ref="A1:K182"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L182"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" customWidth="1"/>
-    <col min="7" max="8" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -931,17 +935,20 @@
       <c r="H1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -965,14 +972,17 @@
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -997,15 +1007,18 @@
       <c r="H3" s="2">
         <v>6</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2" t="b">
-        <v>0</v>
-      </c>
+      <c r="I3" s="2">
+        <v>3</v>
+      </c>
+      <c r="J3" s="2"/>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L3" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1030,17 +1043,20 @@
       <c r="H4">
         <v>6</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
         <v>168</v>
       </c>
-      <c r="J4" t="b">
+      <c r="K4" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="2" t="b">
+      <c r="L4" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1062,14 +1078,14 @@
       <c r="G5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="5">
         <v>96</v>
       </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1091,546 +1107,546 @@
       <c r="G6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>360</v>
       </c>
-      <c r="J6" t="b">
+      <c r="K6" t="b">
         <v>0</v>
       </c>
-      <c r="K6" s="2" t="b">
+      <c r="L6" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I17" s="6"/>
-    </row>
-    <row r="18" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I19" s="6"/>
-    </row>
-    <row r="20" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I21" s="6"/>
-    </row>
-    <row r="22" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I24" s="6"/>
-    </row>
-    <row r="25" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I25" s="6"/>
-    </row>
-    <row r="26" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I26" s="6"/>
-    </row>
-    <row r="27" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I27" s="6"/>
-    </row>
-    <row r="28" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I28" s="6"/>
-    </row>
-    <row r="29" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I29" s="6"/>
-    </row>
-    <row r="30" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I30" s="6"/>
-    </row>
-    <row r="31" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I31" s="6"/>
-    </row>
-    <row r="32" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I33" s="6"/>
-    </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I34" s="6"/>
-    </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I35" s="6"/>
-    </row>
-    <row r="36" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I36" s="6"/>
-    </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I37" s="6"/>
-    </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I38" s="6"/>
-    </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I39" s="6"/>
-    </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I40" s="6"/>
-    </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I41" s="6"/>
-    </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I42" s="6"/>
-    </row>
-    <row r="43" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I43" s="6"/>
-    </row>
-    <row r="44" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I44" s="6"/>
-    </row>
-    <row r="45" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I45" s="6"/>
-    </row>
-    <row r="46" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I46" s="6"/>
-    </row>
-    <row r="47" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I47" s="6"/>
-    </row>
-    <row r="48" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I48" s="6"/>
-    </row>
-    <row r="49" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I49" s="6"/>
-    </row>
-    <row r="50" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I50" s="6"/>
-    </row>
-    <row r="51" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I51" s="6"/>
-    </row>
-    <row r="52" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I52" s="6"/>
-    </row>
-    <row r="53" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I53" s="6"/>
-    </row>
-    <row r="54" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I54" s="6"/>
-    </row>
-    <row r="55" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I55" s="6"/>
-    </row>
-    <row r="56" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I56" s="6"/>
-    </row>
-    <row r="57" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I57" s="6"/>
-    </row>
-    <row r="58" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I58" s="6"/>
-    </row>
-    <row r="59" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I59" s="6"/>
-    </row>
-    <row r="60" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I60" s="6"/>
-    </row>
-    <row r="61" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I61" s="6"/>
-    </row>
-    <row r="62" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I62" s="6"/>
-    </row>
-    <row r="63" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I63" s="6"/>
-    </row>
-    <row r="64" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I64" s="6"/>
-    </row>
-    <row r="65" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I65" s="6"/>
-    </row>
-    <row r="66" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I66" s="6"/>
-    </row>
-    <row r="67" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I67" s="6"/>
-    </row>
-    <row r="68" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I68" s="6"/>
-    </row>
-    <row r="69" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I69" s="6"/>
-    </row>
-    <row r="70" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I70" s="6"/>
-    </row>
-    <row r="71" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I71" s="6"/>
-    </row>
-    <row r="72" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I72" s="6"/>
-    </row>
-    <row r="73" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I73" s="6"/>
-    </row>
-    <row r="74" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I74" s="6"/>
-    </row>
-    <row r="75" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I75" s="6"/>
-    </row>
-    <row r="76" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I76" s="6"/>
-    </row>
-    <row r="77" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I77" s="6"/>
-    </row>
-    <row r="78" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I78" s="6"/>
-    </row>
-    <row r="79" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I79" s="6"/>
-    </row>
-    <row r="80" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I80" s="6"/>
-    </row>
-    <row r="81" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I81" s="6"/>
-    </row>
-    <row r="82" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I82" s="6"/>
-    </row>
-    <row r="83" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I83" s="6"/>
-    </row>
-    <row r="84" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I84" s="6"/>
-    </row>
-    <row r="85" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I85" s="6"/>
-    </row>
-    <row r="86" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I86" s="6"/>
-    </row>
-    <row r="87" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I87" s="6"/>
-    </row>
-    <row r="88" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I88" s="6"/>
-    </row>
-    <row r="89" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I89" s="6"/>
-    </row>
-    <row r="90" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I90" s="6"/>
-    </row>
-    <row r="91" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I91" s="6"/>
-    </row>
-    <row r="92" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I92" s="6"/>
-    </row>
-    <row r="93" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I93" s="6"/>
-    </row>
-    <row r="94" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I94" s="6"/>
-    </row>
-    <row r="95" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I95" s="6"/>
-    </row>
-    <row r="96" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I96" s="6"/>
-    </row>
-    <row r="97" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I97" s="6"/>
-    </row>
-    <row r="98" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I98" s="6"/>
-    </row>
-    <row r="99" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I99" s="6"/>
-    </row>
-    <row r="100" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I100" s="6"/>
-    </row>
-    <row r="101" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I101" s="6"/>
-    </row>
-    <row r="102" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I102" s="6"/>
-    </row>
-    <row r="103" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I103" s="6"/>
-    </row>
-    <row r="104" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I104" s="6"/>
-    </row>
-    <row r="105" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I105" s="6"/>
-    </row>
-    <row r="106" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I106" s="6"/>
-    </row>
-    <row r="107" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I107" s="6"/>
-    </row>
-    <row r="108" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I108" s="6"/>
-    </row>
-    <row r="109" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I109" s="6"/>
-    </row>
-    <row r="110" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I110" s="6"/>
-    </row>
-    <row r="111" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I111" s="6"/>
-    </row>
-    <row r="112" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I112" s="6"/>
-    </row>
-    <row r="113" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I113" s="6"/>
-    </row>
-    <row r="114" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I114" s="6"/>
-    </row>
-    <row r="115" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I115" s="6"/>
-    </row>
-    <row r="116" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I116" s="6"/>
-    </row>
-    <row r="117" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I117" s="6"/>
-    </row>
-    <row r="118" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I118" s="6"/>
-    </row>
-    <row r="119" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I119" s="6"/>
-    </row>
-    <row r="120" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I120" s="6"/>
-    </row>
-    <row r="121" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I121" s="6"/>
-    </row>
-    <row r="122" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I122" s="6"/>
-    </row>
-    <row r="123" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I123" s="6"/>
-    </row>
-    <row r="124" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I124" s="6"/>
-    </row>
-    <row r="125" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I125" s="6"/>
-    </row>
-    <row r="126" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I126" s="6"/>
-    </row>
-    <row r="127" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I127" s="6"/>
-    </row>
-    <row r="128" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I128" s="6"/>
-    </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I129" s="6"/>
-    </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I130" s="6"/>
-    </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I131" s="6"/>
-    </row>
-    <row r="132" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I132" s="6"/>
-    </row>
-    <row r="133" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I133" s="6"/>
-    </row>
-    <row r="134" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I134" s="6"/>
-    </row>
-    <row r="135" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I135" s="6"/>
-    </row>
-    <row r="136" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I136" s="6"/>
-    </row>
-    <row r="137" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I137" s="6"/>
-    </row>
-    <row r="138" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I138" s="6"/>
-    </row>
-    <row r="139" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I139" s="6"/>
-    </row>
-    <row r="140" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I140" s="6"/>
-    </row>
-    <row r="141" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I141" s="6"/>
-    </row>
-    <row r="142" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I142" s="6"/>
-    </row>
-    <row r="143" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I143" s="6"/>
-    </row>
-    <row r="144" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I144" s="6"/>
-    </row>
-    <row r="145" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I145" s="6"/>
-    </row>
-    <row r="146" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I146" s="6"/>
-    </row>
-    <row r="147" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I147" s="6"/>
-    </row>
-    <row r="148" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I148" s="6"/>
-    </row>
-    <row r="149" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I149" s="6"/>
-    </row>
-    <row r="150" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I150" s="6"/>
-    </row>
-    <row r="151" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I151" s="6"/>
-    </row>
-    <row r="152" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I152" s="6"/>
-    </row>
-    <row r="153" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I153" s="6"/>
-    </row>
-    <row r="154" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I154" s="6"/>
-    </row>
-    <row r="155" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I155" s="6"/>
-    </row>
-    <row r="156" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I156" s="6"/>
-    </row>
-    <row r="157" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I157" s="6"/>
-    </row>
-    <row r="158" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I158" s="6"/>
-    </row>
-    <row r="159" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I159" s="6"/>
-    </row>
-    <row r="160" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I160" s="6"/>
-    </row>
-    <row r="161" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I161" s="6"/>
-    </row>
-    <row r="162" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I162" s="6"/>
-    </row>
-    <row r="163" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I163" s="6"/>
-    </row>
-    <row r="164" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I164" s="6"/>
-    </row>
-    <row r="165" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I165" s="6"/>
-    </row>
-    <row r="166" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I166" s="6"/>
-    </row>
-    <row r="167" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I167" s="6"/>
-    </row>
-    <row r="168" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I168" s="6"/>
-    </row>
-    <row r="169" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I169" s="6"/>
-    </row>
-    <row r="170" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I170" s="6"/>
-    </row>
-    <row r="171" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I171" s="6"/>
-    </row>
-    <row r="172" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I172" s="6"/>
-    </row>
-    <row r="173" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I173" s="6"/>
-    </row>
-    <row r="174" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I174" s="6"/>
-    </row>
-    <row r="175" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I175" s="6"/>
-    </row>
-    <row r="176" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I176" s="6"/>
-    </row>
-    <row r="177" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I177" s="6"/>
-    </row>
-    <row r="178" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I178" s="6"/>
-    </row>
-    <row r="179" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I179" s="6"/>
-    </row>
-    <row r="180" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I180" s="6"/>
-    </row>
-    <row r="181" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I181" s="6"/>
-    </row>
-    <row r="182" spans="9:9" x14ac:dyDescent="0.35">
-      <c r="I182" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="6"/>
+    </row>
+    <row r="22" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="6"/>
+    </row>
+    <row r="26" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="6"/>
+    </row>
+    <row r="27" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J30" s="6"/>
+    </row>
+    <row r="31" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J32" s="6"/>
+    </row>
+    <row r="33" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J34" s="6"/>
+    </row>
+    <row r="35" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J35" s="6"/>
+    </row>
+    <row r="36" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J36" s="6"/>
+    </row>
+    <row r="37" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J38" s="6"/>
+    </row>
+    <row r="39" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J39" s="6"/>
+    </row>
+    <row r="40" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J40" s="6"/>
+    </row>
+    <row r="41" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J41" s="6"/>
+    </row>
+    <row r="42" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J42" s="6"/>
+    </row>
+    <row r="43" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J43" s="6"/>
+    </row>
+    <row r="44" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J44" s="6"/>
+    </row>
+    <row r="45" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J45" s="6"/>
+    </row>
+    <row r="46" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J46" s="6"/>
+    </row>
+    <row r="47" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J47" s="6"/>
+    </row>
+    <row r="48" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J48" s="6"/>
+    </row>
+    <row r="49" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J49" s="6"/>
+    </row>
+    <row r="50" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J50" s="6"/>
+    </row>
+    <row r="51" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J51" s="6"/>
+    </row>
+    <row r="52" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J52" s="6"/>
+    </row>
+    <row r="53" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J53" s="6"/>
+    </row>
+    <row r="54" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J54" s="6"/>
+    </row>
+    <row r="55" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J55" s="6"/>
+    </row>
+    <row r="56" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J56" s="6"/>
+    </row>
+    <row r="57" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J57" s="6"/>
+    </row>
+    <row r="58" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J58" s="6"/>
+    </row>
+    <row r="59" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J59" s="6"/>
+    </row>
+    <row r="60" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J60" s="6"/>
+    </row>
+    <row r="61" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J61" s="6"/>
+    </row>
+    <row r="62" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J62" s="6"/>
+    </row>
+    <row r="63" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J63" s="6"/>
+    </row>
+    <row r="64" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J64" s="6"/>
+    </row>
+    <row r="65" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J65" s="6"/>
+    </row>
+    <row r="66" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J66" s="6"/>
+    </row>
+    <row r="67" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J67" s="6"/>
+    </row>
+    <row r="68" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J68" s="6"/>
+    </row>
+    <row r="69" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J69" s="6"/>
+    </row>
+    <row r="70" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J70" s="6"/>
+    </row>
+    <row r="71" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J71" s="6"/>
+    </row>
+    <row r="72" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J72" s="6"/>
+    </row>
+    <row r="73" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J73" s="6"/>
+    </row>
+    <row r="74" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J74" s="6"/>
+    </row>
+    <row r="75" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J75" s="6"/>
+    </row>
+    <row r="76" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J76" s="6"/>
+    </row>
+    <row r="77" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J77" s="6"/>
+    </row>
+    <row r="78" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J78" s="6"/>
+    </row>
+    <row r="79" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J79" s="6"/>
+    </row>
+    <row r="80" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J80" s="6"/>
+    </row>
+    <row r="81" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J81" s="6"/>
+    </row>
+    <row r="82" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J82" s="6"/>
+    </row>
+    <row r="83" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J83" s="6"/>
+    </row>
+    <row r="84" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J84" s="6"/>
+    </row>
+    <row r="85" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J85" s="6"/>
+    </row>
+    <row r="86" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J86" s="6"/>
+    </row>
+    <row r="87" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J87" s="6"/>
+    </row>
+    <row r="88" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J88" s="6"/>
+    </row>
+    <row r="89" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J89" s="6"/>
+    </row>
+    <row r="90" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J90" s="6"/>
+    </row>
+    <row r="91" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J91" s="6"/>
+    </row>
+    <row r="92" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J92" s="6"/>
+    </row>
+    <row r="93" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J93" s="6"/>
+    </row>
+    <row r="94" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J94" s="6"/>
+    </row>
+    <row r="95" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J95" s="6"/>
+    </row>
+    <row r="96" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J96" s="6"/>
+    </row>
+    <row r="97" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J97" s="6"/>
+    </row>
+    <row r="98" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J98" s="6"/>
+    </row>
+    <row r="99" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J99" s="6"/>
+    </row>
+    <row r="100" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J100" s="6"/>
+    </row>
+    <row r="101" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J101" s="6"/>
+    </row>
+    <row r="102" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J102" s="6"/>
+    </row>
+    <row r="103" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J103" s="6"/>
+    </row>
+    <row r="104" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J104" s="6"/>
+    </row>
+    <row r="105" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J105" s="6"/>
+    </row>
+    <row r="106" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J106" s="6"/>
+    </row>
+    <row r="107" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J107" s="6"/>
+    </row>
+    <row r="108" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J108" s="6"/>
+    </row>
+    <row r="109" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J109" s="6"/>
+    </row>
+    <row r="110" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J110" s="6"/>
+    </row>
+    <row r="111" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J111" s="6"/>
+    </row>
+    <row r="112" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J112" s="6"/>
+    </row>
+    <row r="113" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J113" s="6"/>
+    </row>
+    <row r="114" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J114" s="6"/>
+    </row>
+    <row r="115" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J115" s="6"/>
+    </row>
+    <row r="116" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J116" s="6"/>
+    </row>
+    <row r="117" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J117" s="6"/>
+    </row>
+    <row r="118" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J118" s="6"/>
+    </row>
+    <row r="119" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J119" s="6"/>
+    </row>
+    <row r="120" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J120" s="6"/>
+    </row>
+    <row r="121" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J121" s="6"/>
+    </row>
+    <row r="122" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J122" s="6"/>
+    </row>
+    <row r="123" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J123" s="6"/>
+    </row>
+    <row r="124" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J124" s="6"/>
+    </row>
+    <row r="125" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J125" s="6"/>
+    </row>
+    <row r="126" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J126" s="6"/>
+    </row>
+    <row r="127" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J127" s="6"/>
+    </row>
+    <row r="128" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J128" s="6"/>
+    </row>
+    <row r="129" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J129" s="6"/>
+    </row>
+    <row r="130" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J130" s="6"/>
+    </row>
+    <row r="131" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J131" s="6"/>
+    </row>
+    <row r="132" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J132" s="6"/>
+    </row>
+    <row r="133" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J133" s="6"/>
+    </row>
+    <row r="134" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J134" s="6"/>
+    </row>
+    <row r="135" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J135" s="6"/>
+    </row>
+    <row r="136" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J136" s="6"/>
+    </row>
+    <row r="137" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J137" s="6"/>
+    </row>
+    <row r="138" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J138" s="6"/>
+    </row>
+    <row r="139" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J139" s="6"/>
+    </row>
+    <row r="140" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J140" s="6"/>
+    </row>
+    <row r="141" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J141" s="6"/>
+    </row>
+    <row r="142" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J142" s="6"/>
+    </row>
+    <row r="143" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J143" s="6"/>
+    </row>
+    <row r="144" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J144" s="6"/>
+    </row>
+    <row r="145" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J145" s="6"/>
+    </row>
+    <row r="146" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J146" s="6"/>
+    </row>
+    <row r="147" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J147" s="6"/>
+    </row>
+    <row r="148" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J148" s="6"/>
+    </row>
+    <row r="149" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J149" s="6"/>
+    </row>
+    <row r="150" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J150" s="6"/>
+    </row>
+    <row r="151" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J151" s="6"/>
+    </row>
+    <row r="152" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J152" s="6"/>
+    </row>
+    <row r="153" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J153" s="6"/>
+    </row>
+    <row r="154" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J154" s="6"/>
+    </row>
+    <row r="155" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J155" s="6"/>
+    </row>
+    <row r="156" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J156" s="6"/>
+    </row>
+    <row r="157" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J157" s="6"/>
+    </row>
+    <row r="158" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J158" s="6"/>
+    </row>
+    <row r="159" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J159" s="6"/>
+    </row>
+    <row r="160" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J160" s="6"/>
+    </row>
+    <row r="161" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J161" s="6"/>
+    </row>
+    <row r="162" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J162" s="6"/>
+    </row>
+    <row r="163" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J163" s="6"/>
+    </row>
+    <row r="164" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J164" s="6"/>
+    </row>
+    <row r="165" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J165" s="6"/>
+    </row>
+    <row r="166" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J166" s="6"/>
+    </row>
+    <row r="167" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J167" s="6"/>
+    </row>
+    <row r="168" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J168" s="6"/>
+    </row>
+    <row r="169" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J169" s="6"/>
+    </row>
+    <row r="170" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J170" s="6"/>
+    </row>
+    <row r="171" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J171" s="6"/>
+    </row>
+    <row r="172" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J172" s="6"/>
+    </row>
+    <row r="173" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J173" s="6"/>
+    </row>
+    <row r="174" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J174" s="6"/>
+    </row>
+    <row r="175" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J175" s="6"/>
+    </row>
+    <row r="176" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J176" s="6"/>
+    </row>
+    <row r="177" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J177" s="6"/>
+    </row>
+    <row r="178" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J178" s="6"/>
+    </row>
+    <row r="179" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J179" s="6"/>
+    </row>
+    <row r="180" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J180" s="6"/>
+    </row>
+    <row r="181" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J181" s="6"/>
+    </row>
+    <row r="182" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J182" s="6"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:F6">
@@ -1643,7 +1659,7 @@
       <formula>IF(AND(NOT(ISBLANK($A3)),ISBLANK(E3)),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:H6">
+  <conditionalFormatting sqref="G4:I6">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND(NOT(ISBLANK($E4)),$E4="Specific month",ISBLANK(G4))</formula>
     </cfRule>
@@ -1651,7 +1667,7 @@
       <formula>$E4="Never repair"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H6">
+  <conditionalFormatting sqref="H4:I6">
     <cfRule type="expression" dxfId="0" priority="3">
       <formula>$E4="Immediately"</formula>
     </cfRule>
@@ -1660,14 +1676,14 @@
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D6" xr:uid="{D6BF9489-3E0C-4141-AE1B-F8FA18EB1107}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H6" xr:uid="{A4E0C563-791F-473E-957D-7529E736E607}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:I6" xr:uid="{A4E0C563-791F-473E-957D-7529E736E607}">
       <formula1>1</formula1>
       <formula2>12</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E6" xr:uid="{497BB2C1-8657-4904-B309-5421697BEB34}">
       <formula1>"Immediately, Specific month, Never repair"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I140" xr:uid="{1FF2B63A-484C-4FE4-BEA2-589F2FE2EAFA}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J140" xr:uid="{1FF2B63A-484C-4FE4-BEA2-589F2FE2EAFA}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F6" xr:uid="{4FCD0DC3-1F3E-4A0E-88E5-237259ABD7EA}">
